--- a/deliverables/hamilton/HamiltonUnited_2010B_WeekByWeek_2026-27.xlsx
+++ b/deliverables/hamilton/HamiltonUnited_2010B_WeekByWeek_2026-27.xlsx
@@ -10,13 +10,14 @@
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Year Plan" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sessions" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Week Template" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Principles" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sessions" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Week Template" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Sessions!$A$4:$L$52</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Year Plan'!$A$4:$Q$56</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Sessions!$A$4:$M$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Year Plan'!$A$4:$R$56</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="O4" authorId="0">
+    <comment ref="P4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="798">
   <si>
     <t xml:space="preserve">Hamilton United 2010 Boys OPDL — Week-by-Week Plan 2026/27</t>
   </si>
@@ -64,7 +65,13 @@
     <t xml:space="preserve">Year Plan</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per week: phase, theme, moments, weekly objective and what each training day looks like.</t>
+    <t xml:space="preserve">One row per week: phase, theme, moments, the core principles trained, weekly objective and what each training day looks like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 23 core principles from the game model chart: when each is installed, how many weeks train it, and the first week (formulas).</t>
   </si>
   <si>
     <t xml:space="preserve">Sessions</t>
@@ -163,6 +170,9 @@
     <t xml:space="preserve">Session obj. #</t>
   </si>
   <si>
+    <t xml:space="preserve">Core principles trained</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weekly objective</t>
   </si>
   <si>
@@ -208,6 +218,9 @@
     <t xml:space="preserve">3, 6</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Purpose · AO Width/depth · AO Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create passing options around, through and beyond the opposition.</t>
   </si>
   <si>
@@ -232,6 +245,9 @@
     <t xml:space="preserve">Baseline week: film the Saturday game for the November baseline</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Overloads · AO Support · AO Purpose</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create and exploit numerical advantages to progress the ball forward.</t>
   </si>
   <si>
@@ -247,6 +263,9 @@
     <t xml:space="preserve">2, 3</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Play through/around/over · AO Width/depth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to progress the ball by recognizing when to play through, around or over the opposition.</t>
   </si>
   <si>
@@ -265,6 +284,9 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Compact</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to prevent the opposition from progressing through central areas.</t>
   </si>
   <si>
@@ -277,6 +299,9 @@
     <t xml:space="preserve">Recovery runs: lose the ball, sprint back inside; 5 reps x 3</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Purpose · AO Support · DO Compact</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create passing options and defend forward through compactness and pressure.</t>
   </si>
   <si>
@@ -304,6 +329,9 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Combinations · AO Runners in front &amp; behind</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to break lines through purposeful movement and combination play.</t>
   </si>
   <si>
@@ -319,6 +347,9 @@
     <t xml:space="preserve">Strength, aerobic base</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Manipulate · AO Runners in front &amp; behind · DO Make play predictable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create space by manipulating the opposition’s defensive structure.</t>
   </si>
   <si>
@@ -364,6 +395,9 @@
     <t xml:space="preserve">Win it back</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Press · DO Step forward · DO Win high</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to regain possession by coordinating pressure around the ball.</t>
   </si>
   <si>
@@ -385,6 +419,9 @@
     <t xml:space="preserve">7</t>
   </si>
   <si>
+    <t xml:space="preserve">DT React &amp; repress · DT Contact · DT Deny</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to immediately regain possession following a loss of the ball.</t>
   </si>
   <si>
@@ -397,6 +434,9 @@
     <t xml:space="preserve">Repeat sprints: transition runs, 6 x 20 yd</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Make play predictable · DO Press · DO Win high</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to force the opposition into predictable areas to regain possession.</t>
   </si>
   <si>
@@ -412,6 +452,9 @@
     <t xml:space="preserve">DT + DO</t>
   </si>
   <si>
+    <t xml:space="preserve">DT Recover shape · DT Deny · DO Protect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to delay the opposition’s attack and protect the space behind.</t>
   </si>
   <si>
@@ -436,6 +479,9 @@
     <t xml:space="preserve">5, 7</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Purpose · AO Overloads · DT React &amp; repress</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to connect building with an immediate reaction when we lose the ball.</t>
   </si>
   <si>
@@ -454,6 +500,9 @@
     <t xml:space="preserve">5, 6</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Press · AT Forward · AT Exploit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to win the ball and attack before the opposition reorganizes.</t>
   </si>
   <si>
@@ -472,6 +521,9 @@
     <t xml:space="preserve">4, 7</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Runners in front &amp; behind · AO Combinations · DT Recover shape</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to finish attacks while protecting against the counter.</t>
   </si>
   <si>
@@ -484,6 +536,9 @@
     <t xml:space="preserve">Repeat sprints 6 x 30 yd</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Step forward · DO Win high · AT Forward</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to regain the ball high and turn it into a goal.</t>
   </si>
   <si>
@@ -511,6 +566,9 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
+    <t xml:space="preserve">AT Forward · AT Exploit · AT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to exploit numerical advantages immediately after winning possession.</t>
   </si>
   <si>
@@ -535,13 +593,16 @@
     <t xml:space="preserve">Pre-season begins</t>
   </si>
   <si>
-    <t xml:space="preserve">Find ways to progress forward quickly before the opposition can reorganize.</t>
+    <t xml:space="preserve">AT Forward · AT Space · AT Support · AT Secure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find ways to progress forward quickly before the opposition can reorganize, and to secure possession when the attack is not on.</t>
   </si>
   <si>
     <t xml:space="preserve">5v5 + 2: switch on the regain</t>
   </si>
   <si>
-    <t xml:space="preserve">KEY SESSION · Progress before they reorganize (see Sessions tab)</t>
+    <t xml:space="preserve">KEY SESSION · Go now, or secure (see Sessions tab)</t>
   </si>
   <si>
     <t xml:space="preserve">Speed endurance 8 x 40 yd</t>
@@ -550,6 +611,9 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Runners in front &amp; behind · AT Space</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create final actions by getting behind the opposition’s back line.</t>
   </si>
   <si>
@@ -565,6 +629,9 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Runners in front &amp; behind · AO Width/depth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to attack the box with purposeful movements and coordinated runs.</t>
   </si>
   <si>
@@ -577,6 +644,9 @@
     <t xml:space="preserve">Finishing volume</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Combinations · AO Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create finishing opportunities through quick combinations around the box.</t>
   </si>
   <si>
@@ -598,6 +668,9 @@
     <t xml:space="preserve">1–7</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Purpose · AT Secure · DO Compact · DT React &amp; repress</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to execute all four moments against different problems.</t>
   </si>
   <si>
@@ -613,6 +686,9 @@
     <t xml:space="preserve">Taper to game speed</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Overloads · AO Play through/around/over · AO Purpose</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to beat a high press with the 1-3-2 build.</t>
   </si>
   <si>
@@ -628,6 +704,9 @@
     <t xml:space="preserve">2, 4</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Manipulate · AO Width/depth · AO Combinations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create chances against a low block.</t>
   </si>
   <si>
@@ -643,6 +722,9 @@
     <t xml:space="preserve">All 4 + set pieces</t>
   </si>
   <si>
+    <t xml:space="preserve">Set pieces · AO Purpose</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to bring the whole game model into match conditions.</t>
   </si>
   <si>
@@ -667,6 +749,9 @@
     <t xml:space="preserve">Compete with identity</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Play through/around/over · AO Overloads</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to progress against different pressing shapes.</t>
   </si>
   <si>
@@ -721,6 +806,9 @@
     <t xml:space="preserve">Speed + defending set pieces</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Combinations · AO Manipulate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to break lines against a mid block.</t>
   </si>
   <si>
@@ -736,6 +824,9 @@
     <t xml:space="preserve">Jun</t>
   </si>
   <si>
+    <t xml:space="preserve">AT Forward · AT Exploit · AT Space · AT Secure</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create goal-scoring opportunities within the first few actions after regaining possession.</t>
   </si>
   <si>
@@ -745,6 +836,9 @@
     <t xml:space="preserve">KEY SESSION · Counter after the regain (see Sessions tab)</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Compact · DO Protect · DO Step forward · DO Win high</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to defend forward through compactness and pressure.</t>
   </si>
   <si>
@@ -784,6 +878,9 @@
     <t xml:space="preserve">2, 6</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Width/depth · AO Support · DO Compact</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to apply our principles in the 1-4-2-3-1.</t>
   </si>
   <si>
@@ -793,6 +890,9 @@
     <t xml:space="preserve">Maintain; then rest</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Manipulate · DO Make play predictable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to switch shape during a game.</t>
   </si>
   <si>
@@ -814,6 +914,9 @@
     <t xml:space="preserve">Aug</t>
   </si>
   <si>
+    <t xml:space="preserve">AT Support · DT Recover shape</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to reload fitness through game-based work.</t>
   </si>
   <si>
@@ -835,24 +938,36 @@
     <t xml:space="preserve">Reload week</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Overloads · AO Runners in front &amp; behind</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to exploit a back four with our structure.</t>
   </si>
   <si>
     <t xml:space="preserve">KEY SESSION · Game plan vs a back four (see Sessions tab)</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Width/depth · AO Manipulate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to beat a back three.</t>
   </si>
   <si>
     <t xml:space="preserve">KEY SESSION · Game plan vs a back three (see Sessions tab)</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Combinations · AO Play through/around/over</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to break lines in either system.</t>
   </si>
   <si>
     <t xml:space="preserve">KEY SESSION · Breaking lines in both systems (see Sessions tab)</t>
   </si>
   <si>
+    <t xml:space="preserve">DO Press · DO Make play predictable · DO Step forward</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to press as a unit in either system.</t>
   </si>
   <si>
@@ -874,6 +989,9 @@
     <t xml:space="preserve">6, 7</t>
   </si>
   <si>
+    <t xml:space="preserve">AT Secure · DO Compact · DO Protect · AO Purpose</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to manage a game when we are winning.</t>
   </si>
   <si>
@@ -886,12 +1004,18 @@
     <t xml:space="preserve">1, 5</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Runners in front &amp; behind · DO Win high</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to create chances when we are losing.</t>
   </si>
   <si>
     <t xml:space="preserve">KEY SESSION · Chase a game (see Sessions tab)</t>
   </si>
   <si>
+    <t xml:space="preserve">AT Forward · AT Exploit · AT Support · AT Space</t>
+  </si>
+  <si>
     <t xml:space="preserve">KEY SESSION · Sharpen the counter (see Sessions tab)</t>
   </si>
   <si>
@@ -904,6 +1028,9 @@
     <t xml:space="preserve">Oct</t>
   </si>
   <si>
+    <t xml:space="preserve">DT React &amp; repress · DT Contact · DT Deny · DT Recover shape</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways for players to solve problems without the coach.</t>
   </si>
   <si>
@@ -916,6 +1043,9 @@
     <t xml:space="preserve">Peak, then active rest</t>
   </si>
   <si>
+    <t xml:space="preserve">AO Purpose · DO Press · DT React &amp; repress · AT Secure</t>
+  </si>
+  <si>
     <t xml:space="preserve">Find ways to execute our identity in the final games.</t>
   </si>
   <si>
@@ -943,6 +1073,243 @@
     <t xml:space="preserve">Blue = planning inputs (edit). Competition dates and the mid-season break are placeholders: confirm against the OPDL fixture list.</t>
   </si>
   <si>
+    <t xml:space="preserve">Core principles — coverage across the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 23 principles from the game model chart. Weeks trained and first week are formulas on the Year Plan’s “Core principles trained” column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag (as used on Year Plan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it means</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installed (month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weeks trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First week trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First week of (Mon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possession with purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overloads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Overloads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create &amp; exploit overloads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play through/around/over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Play through/around/over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play through, around, or over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Width/depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Width/depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintain width &amp; depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runners in front &amp; behind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Runners in front &amp; behind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make runs to receive or attack in behind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support &amp; passing options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Combinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-man combinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manipulate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO Manipulate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play across the game channel to move opposition players and create space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT Forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First look forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT Exploit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack disorganization quickly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support the attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploit open space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT Secure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure possession if immediate attack is not on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compact centrally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make play predictable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO Make play predictable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Force wide or inside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Press as a unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect between lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO Step forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step forward aggressively</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO Win high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win the ball in advanced areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">React &amp; repress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT React &amp; repress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">React immediately and repress to win the ball back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make contact / close down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT Deny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deny forward passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recover shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT Recover shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recover shape quickly if unable to win the ball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principles never trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installed month = when the principle is first taught as the main focus (periodization deck, slide 8). Earlier weeks may preview it, e.g. counters in February before AT is installed in March.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sessions — the example key session for each week (Wednesday, MD-3, 90 min)</t>
   </si>
   <si>
@@ -955,6 +1322,9 @@
     <t xml:space="preserve">Session title</t>
   </si>
   <si>
+    <t xml:space="preserve">Core principles</t>
+  </si>
+  <si>
     <t xml:space="preserve">Session objective</t>
   </si>
   <si>
@@ -1099,9 +1469,6 @@
     <t xml:space="preserve">Where can I position myself to help the team?</t>
   </si>
   <si>
-    <t xml:space="preserve">Third-man combinations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Receive between the lines with an open body · Use the third player to break a line · Play forward quickly</t>
   </si>
   <si>
@@ -1201,9 +1568,6 @@
     <t xml:space="preserve">Losing the ball: is it the start of our defending?</t>
   </si>
   <si>
-    <t xml:space="preserve">Make play predictable</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curved runs to show one way · Lock the side · Trap near the touchline</t>
   </si>
   <si>
@@ -1360,22 +1724,22 @@
     <t xml:space="preserve">Is it on? Go!</t>
   </si>
   <si>
-    <t xml:space="preserve">Progress before they reorganize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward movement before they recover · Support the ball carrier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ball reaches the final third within 10 s of a regain</t>
+    <t xml:space="preserve">Go now, or secure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward movement before they recover · Support the ball carrier · Recognize when it is not on and secure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ball reaches the final third within 10 s of a regain, or is kept (no turnover) when forward is closed</t>
   </si>
   <si>
     <t xml:space="preserve">Running with the ball + combination play</t>
   </si>
   <si>
-    <t xml:space="preserve">6v4 counter channel game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11v11 transition game: regain → final third in 10 s</t>
+    <t xml:space="preserve">6v4 counter channel game: if the forward pass is blocked, 3 passes to secure = 1 point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11v11 transition game: regain → final third in 10 s, or secure and reset into the 1-3-4-3</t>
   </si>
   <si>
     <t xml:space="preserve">Can we get there before they do?</t>
@@ -1928,9 +2292,6 @@
   </si>
   <si>
     <t xml:space="preserve">Match-day code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose</t>
   </si>
   <si>
     <t xml:space="preserve">Space &amp; numbers</t>
@@ -2090,12 +2451,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mmm\ d&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2261,6 +2623,34 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF2F5FB8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F7543"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFA50D26"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFA55A12"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2387,7 +2777,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2568,12 +2958,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2584,7 +2982,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2596,7 +3014,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3126,11 +3544,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30946201"/>
-        <c:axId val="35685049"/>
+        <c:axId val="60931010"/>
+        <c:axId val="93280788"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30946201"/>
+        <c:axId val="60931010"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3162,7 +3580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35685049"/>
+        <c:crossAx val="93280788"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3170,7 +3588,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35685049"/>
+        <c:axId val="93280788"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3248,7 +3666,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30946201"/>
+        <c:crossAx val="60931010"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3546,7 +3964,7 @@
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -3562,7 +3980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -3579,16 +3997,16 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
@@ -3598,80 +4016,88 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+    </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3690,7 +4116,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3700,76 +4126,80 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3780,49 +4210,52 @@
         <v>46328</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="15" t="n">
+      <c r="Q5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" s="11" t="s">
-        <v>59</v>
+      <c r="R5" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3833,48 +4266,51 @@
         <v>46335</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="O6" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="15" t="n">
+      <c r="P6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="P6" s="15" t="n">
+      <c r="Q6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="n">
@@ -3884,48 +4320,51 @@
         <v>46342</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="P7" s="15" t="n">
+      <c r="Q7" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="n">
@@ -3935,48 +4374,51 @@
         <v>46349</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="P8" s="15" t="n">
+      <c r="Q8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="n">
@@ -3986,49 +4428,52 @@
         <v>46356</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>75</v>
+        <v>54</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="15" t="n">
+      <c r="Q9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="11" t="s">
-        <v>79</v>
+      <c r="R9" s="11" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4039,48 +4484,51 @@
         <v>46363</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>84</v>
+        <v>91</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>87</v>
+        <v>57</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" s="15" t="n">
         <v>3.5</v>
       </c>
-      <c r="P10" s="15" t="n">
+      <c r="Q10" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
@@ -4090,49 +4538,52 @@
         <v>46370</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>89</v>
+        <v>69</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>92</v>
+        <v>57</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O11" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="15" t="n">
         <v>3.5</v>
       </c>
-      <c r="P11" s="15" t="n">
+      <c r="Q11" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q11" s="11" t="s">
-        <v>93</v>
+      <c r="R11" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4143,49 +4594,52 @@
         <v>46377</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>96</v>
+        <v>105</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="15" t="n">
-        <v>1</v>
       </c>
       <c r="P12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" s="11" t="s">
-        <v>98</v>
+      <c r="Q12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4196,49 +4650,52 @@
         <v>46384</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="O13" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="P13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="11" t="s">
-        <v>100</v>
+      <c r="Q13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4249,48 +4706,51 @@
         <v>46391</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>104</v>
+        <v>76</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>107</v>
+        <v>57</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="O14" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="O14" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="P14" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P14" s="21" t="n">
+      <c r="Q14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="n">
@@ -4300,48 +4760,51 @@
         <v>46398</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>111</v>
+        <v>121</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>122</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>114</v>
+        <v>57</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>125</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="O15" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="O15" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="P15" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P15" s="21" t="n">
+      <c r="Q15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="n">
@@ -4351,48 +4814,51 @@
         <v>46405</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>115</v>
+        <v>76</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>118</v>
+        <v>57</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="O16" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="P16" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P16" s="21" t="n">
+      <c r="Q16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="n">
@@ -4402,48 +4868,51 @@
         <v>46412</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F17" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="O17" s="21" t="n">
+      <c r="P17" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P17" s="21" t="n">
+      <c r="Q17" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="n">
@@ -4453,48 +4922,51 @@
         <v>46419</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>128</v>
+        <v>141</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>142</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>131</v>
+        <v>57</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>145</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>3.5</v>
+        <v>61</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="P18" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="n">
@@ -4504,49 +4976,52 @@
         <v>46426</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>134</v>
+        <v>148</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>149</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>137</v>
+        <v>57</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>152</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="O19" s="21" t="n">
-        <v>3.5</v>
+        <v>61</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="P19" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q19" s="17" t="s">
-        <v>138</v>
+      <c r="Q19" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R19" s="17" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4557,48 +5032,51 @@
         <v>46433</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>140</v>
+        <v>155</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>143</v>
+        <v>57</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>159</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>3.5</v>
+        <v>61</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="P20" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q20" s="17"/>
+      <c r="Q20" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="n">
@@ -4608,48 +5086,51 @@
         <v>46440</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>161</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="K21" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="L21" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" s="17" t="s">
         <v>147</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="O21" s="21" t="n">
-        <v>3.5</v>
       </c>
       <c r="P21" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q21" s="17"/>
+      <c r="Q21" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
@@ -4659,49 +5140,52 @@
         <v>46447</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>153</v>
+        <v>170</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>157</v>
+        <v>173</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O22" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="P22" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="P22" s="27" t="n">
+      <c r="Q22" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q22" s="23" t="s">
-        <v>160</v>
+      <c r="R22" s="23" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4712,48 +5196,51 @@
         <v>46454</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>161</v>
+        <v>170</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>164</v>
+        <v>173</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="L23" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O23" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="P23" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="P23" s="27" t="n">
+      <c r="Q23" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="n">
@@ -4763,48 +5250,51 @@
         <v>46461</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>166</v>
+        <v>185</v>
+      </c>
+      <c r="H24" s="26" t="s">
+        <v>186</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="K24" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="L24" s="23" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>189</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O24" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="P24" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="P24" s="27" t="n">
+      <c r="Q24" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
@@ -4814,48 +5304,51 @@
         <v>46468</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>171</v>
+        <v>191</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="K25" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="L25" s="23" t="s">
-        <v>174</v>
+      <c r="K25" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="N25" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O25" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="P25" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="P25" s="27" t="n">
+      <c r="Q25" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
     </row>
     <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="n">
@@ -4865,48 +5358,51 @@
         <v>46475</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>175</v>
+        <v>191</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>197</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="K26" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="L26" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="N26" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="L26" s="23" t="s">
+      <c r="O26" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="O26" s="27" t="n">
+      <c r="P26" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="P26" s="27" t="n">
+      <c r="Q26" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="n">
@@ -4916,48 +5412,51 @@
         <v>46482</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>182</v>
+        <v>204</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="J27" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="K27" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="23" t="s">
-        <v>185</v>
+        <v>173</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>208</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="N27" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="O27" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O27" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P27" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P27" s="27" t="n">
+      <c r="Q27" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
     </row>
     <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="n">
@@ -4967,48 +5466,51 @@
         <v>46489</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>187</v>
+        <v>69</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="K28" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="L28" s="23" t="s">
-        <v>190</v>
+        <v>173</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="N28" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="O28" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P28" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P28" s="27" t="n">
+      <c r="Q28" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
     </row>
     <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="n">
@@ -5018,48 +5520,51 @@
         <v>46496</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>192</v>
+        <v>216</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="K29" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>195</v>
+        <v>173</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="N29" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="O29" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O29" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P29" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P29" s="27" t="n">
+      <c r="Q29" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="n">
@@ -5069,49 +5574,52 @@
         <v>46503</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>197</v>
+        <v>204</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>223</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="J30" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="L30" s="23" t="s">
-        <v>200</v>
+        <v>173</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
       <c r="N30" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="O30" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="O30" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P30" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P30" s="27" t="n">
+      <c r="Q30" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="Q30" s="23" t="s">
-        <v>201</v>
+      <c r="R30" s="23" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5122,49 +5630,52 @@
         <v>46510</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>205</v>
+        <v>91</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>232</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="J31" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="K31" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="L31" s="29" t="s">
-        <v>208</v>
+        <v>234</v>
+      </c>
+      <c r="K31" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" s="32" t="s">
+        <v>235</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O31" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O31" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P31" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="33" t="n">
+      <c r="Q31" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q31" s="29" t="s">
-        <v>211</v>
+      <c r="R31" s="29" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5175,48 +5686,51 @@
         <v>46517</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>212</v>
+        <v>191</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>192</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="J32" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="K32" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>213</v>
+        <v>234</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="L32" s="32" t="s">
+        <v>195</v>
       </c>
       <c r="M32" s="29" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="N32" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O32" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O32" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P32" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P32" s="33" t="n">
+      <c r="Q32" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
     </row>
     <row r="33" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="n">
@@ -5226,48 +5740,51 @@
         <v>46524</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>215</v>
+        <v>105</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>242</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="J33" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="L33" s="29" t="s">
-        <v>218</v>
+        <v>234</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="L33" s="32" t="s">
+        <v>245</v>
       </c>
       <c r="M33" s="29" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O33" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O33" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P33" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" s="33" t="n">
+      <c r="Q33" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
     </row>
     <row r="34" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="n">
@@ -5277,48 +5794,51 @@
         <v>46531</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>219</v>
+        <v>105</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>242</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="J34" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="K34" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="L34" s="29" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L34" s="32" t="s">
+        <v>249</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="N34" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O34" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O34" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P34" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="33" t="n">
+      <c r="Q34" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
     </row>
     <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="n">
@@ -5328,48 +5848,51 @@
         <v>46538</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>223</v>
+        <v>91</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>251</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="J35" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="K35" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="L35" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K35" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="L35" s="32" t="s">
+        <v>254</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O35" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O35" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P35" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P35" s="33" t="n">
+      <c r="Q35" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
     </row>
     <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="n">
@@ -5379,48 +5902,51 @@
         <v>46545</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>228</v>
+        <v>170</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>257</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="K36" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="L36" s="32" t="s">
+        <v>260</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O36" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O36" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P36" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P36" s="33" t="n">
+      <c r="Q36" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
     </row>
     <row r="37" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="n">
@@ -5430,48 +5956,51 @@
         <v>46552</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>231</v>
+        <v>76</v>
+      </c>
+      <c r="H37" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="I37" s="29" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="K37" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="L37" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K37" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="L37" s="32" t="s">
+        <v>264</v>
       </c>
       <c r="M37" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N37" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O37" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O37" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P37" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P37" s="33" t="n">
+      <c r="Q37" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
     </row>
     <row r="38" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="n">
@@ -5481,48 +6010,51 @@
         <v>46559</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>111</v>
+        <v>121</v>
+      </c>
+      <c r="H38" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="J38" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="K38" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="L38" s="29" t="s">
-        <v>226</v>
+      <c r="K38" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="L38" s="32" t="s">
+        <v>266</v>
       </c>
       <c r="M38" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N38" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O38" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O38" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="P38" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P38" s="33" t="n">
+      <c r="Q38" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
     </row>
     <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="n">
@@ -5532,49 +6064,52 @@
         <v>46566</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>236</v>
+        <v>191</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>197</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="J39" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="L39" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="M39" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="N39" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="K39" s="32" t="s">
+      <c r="O39" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="L39" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="M39" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="N39" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="O39" s="33" t="n">
+      <c r="P39" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P39" s="33" t="n">
+      <c r="Q39" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q39" s="29" t="s">
-        <v>239</v>
+      <c r="R39" s="29" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5585,48 +6120,51 @@
         <v>46573</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>244</v>
+        <v>274</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>275</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K40" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="L40" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K40" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="L40" s="40" t="s">
+        <v>277</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N40" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="O40" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O40" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="P40" s="41" t="n">
         <v>2.5</v>
       </c>
-      <c r="P40" s="41" t="n">
+      <c r="Q40" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" s="37"/>
+      <c r="R40" s="37"/>
     </row>
     <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="n">
@@ -5636,48 +6174,51 @@
         <v>46580</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>247</v>
+        <v>274</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>279</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="K41" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="L41" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="L41" s="40" t="s">
+        <v>282</v>
       </c>
       <c r="M41" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N41" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="O41" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O41" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="P41" s="41" t="n">
         <v>2.5</v>
       </c>
-      <c r="P41" s="41" t="n">
+      <c r="Q41" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q41" s="37"/>
+      <c r="R41" s="37"/>
     </row>
     <row r="42" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="n">
@@ -5687,49 +6228,52 @@
         <v>46587</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>105</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L42" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M42" s="37" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="N42" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="O42" s="41" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="O42" s="37" t="s">
+        <v>283</v>
       </c>
       <c r="P42" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="37" t="s">
-        <v>251</v>
+      <c r="Q42" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="37" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5740,49 +6284,52 @@
         <v>46594</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="H43" s="40" t="s">
+        <v>105</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L43" s="37" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M43" s="37" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="N43" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="O43" s="41" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="O43" s="37" t="s">
+        <v>283</v>
       </c>
       <c r="P43" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="37" t="s">
-        <v>252</v>
+      <c r="Q43" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="37" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5793,49 +6340,52 @@
         <v>46601</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>254</v>
+        <v>204</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>287</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="K44" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="L44" s="37" t="s">
-        <v>257</v>
+        <v>234</v>
+      </c>
+      <c r="K44" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="L44" s="40" t="s">
+        <v>290</v>
       </c>
       <c r="M44" s="37" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="N44" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="O44" s="41" t="n">
+        <v>292</v>
+      </c>
+      <c r="O44" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="P44" s="41" t="n">
         <v>3.5</v>
       </c>
-      <c r="P44" s="41" t="n">
+      <c r="Q44" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q44" s="37" t="s">
-        <v>260</v>
+      <c r="R44" s="37" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5846,48 +6396,51 @@
         <v>46608</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>261</v>
+        <v>274</v>
+      </c>
+      <c r="H45" s="40" t="s">
+        <v>295</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K45" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="L45" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K45" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="L45" s="40" t="s">
+        <v>297</v>
       </c>
       <c r="M45" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N45" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="O45" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O45" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="P45" s="41" t="n">
         <v>3.5</v>
       </c>
-      <c r="P45" s="41" t="n">
+      <c r="Q45" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
     </row>
     <row r="46" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="37" t="n">
@@ -5897,48 +6450,51 @@
         <v>46615</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>263</v>
+        <v>274</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>298</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K46" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="L46" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="L46" s="40" t="s">
+        <v>300</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="O46" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O46" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="P46" s="41" t="n">
         <v>3.5</v>
       </c>
-      <c r="P46" s="41" t="n">
+      <c r="Q46" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
     </row>
     <row r="47" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="37" t="n">
@@ -5948,48 +6504,51 @@
         <v>46622</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E47" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>265</v>
+        <v>91</v>
+      </c>
+      <c r="H47" s="40" t="s">
+        <v>301</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>206</v>
+        <v>302</v>
       </c>
       <c r="J47" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="K47" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="L47" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K47" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="L47" s="40" t="s">
+        <v>303</v>
       </c>
       <c r="M47" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N47" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="O47" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O47" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="P47" s="41" t="n">
         <v>3.5</v>
       </c>
-      <c r="P47" s="41" t="n">
+      <c r="Q47" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
     </row>
     <row r="48" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="37" t="n">
@@ -5999,48 +6558,51 @@
         <v>46629</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>267</v>
+        <v>76</v>
+      </c>
+      <c r="H48" s="40" t="s">
+        <v>304</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="K48" s="40" t="s">
-        <v>269</v>
-      </c>
-      <c r="L48" s="37" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K48" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="L48" s="40" t="s">
+        <v>307</v>
       </c>
       <c r="M48" s="37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N48" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="O48" s="41" t="n">
+        <v>237</v>
+      </c>
+      <c r="O48" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="P48" s="41" t="n">
         <v>3.5</v>
       </c>
-      <c r="P48" s="41" t="n">
+      <c r="Q48" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" s="37"/>
+      <c r="R48" s="37"/>
     </row>
     <row r="49" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="29" t="n">
@@ -6050,48 +6612,51 @@
         <v>46636</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>274</v>
+        <v>311</v>
+      </c>
+      <c r="H49" s="32" t="s">
+        <v>312</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="J49" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="K49" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="L49" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K49" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L49" s="32" t="s">
+        <v>314</v>
       </c>
       <c r="M49" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N49" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="O49" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O49" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="P49" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P49" s="33" t="n">
+      <c r="Q49" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
     </row>
     <row r="50" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="n">
@@ -6101,48 +6666,51 @@
         <v>46643</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G50" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>278</v>
+        <v>316</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>317</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="J50" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="K50" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="L50" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K50" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L50" s="32" t="s">
+        <v>319</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N50" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="O50" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O50" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="P50" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P50" s="33" t="n">
+      <c r="Q50" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
     </row>
     <row r="51" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="n">
@@ -6152,48 +6720,51 @@
         <v>46650</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F51" s="34" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G51" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>153</v>
+        <v>170</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>320</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="J51" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="K51" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="L51" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="L51" s="32" t="s">
+        <v>321</v>
       </c>
       <c r="M51" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N51" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="O51" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O51" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="P51" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P51" s="33" t="n">
+      <c r="Q51" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
     </row>
     <row r="52" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="n">
@@ -6203,48 +6774,51 @@
         <v>46657</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>281</v>
+        <v>191</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="J52" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="K52" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L52" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K52" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="L52" s="32" t="s">
+        <v>323</v>
       </c>
       <c r="M52" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N52" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="O52" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O52" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="P52" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="P52" s="33" t="n">
+      <c r="Q52" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
     </row>
     <row r="53" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="29" t="n">
@@ -6254,48 +6828,51 @@
         <v>46664</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G53" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>284</v>
+        <v>121</v>
+      </c>
+      <c r="H53" s="32" t="s">
+        <v>325</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>206</v>
+        <v>326</v>
       </c>
       <c r="J53" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="K53" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="L53" s="29" t="s">
-        <v>226</v>
+        <v>234</v>
+      </c>
+      <c r="K53" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="L53" s="32" t="s">
+        <v>328</v>
       </c>
       <c r="M53" s="29" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="N53" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="O53" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="O53" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="P53" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="P53" s="33" t="n">
+      <c r="Q53" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="29"/>
+      <c r="R53" s="29"/>
     </row>
     <row r="54" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="29" t="n">
@@ -6305,48 +6882,51 @@
         <v>46671</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>288</v>
+        <v>204</v>
+      </c>
+      <c r="H54" s="32" t="s">
+        <v>330</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="K54" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="L54" s="29" t="s">
-        <v>290</v>
+        <v>234</v>
+      </c>
+      <c r="K54" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L54" s="32" t="s">
+        <v>332</v>
       </c>
       <c r="M54" s="29" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="N54" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="O54" s="33" t="n">
+        <v>334</v>
+      </c>
+      <c r="O54" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="P54" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="P54" s="33" t="n">
+      <c r="Q54" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
     </row>
     <row r="55" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="29" t="n">
@@ -6356,49 +6936,52 @@
         <v>46678</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>292</v>
+        <v>105</v>
+      </c>
+      <c r="H55" s="32" t="s">
+        <v>105</v>
       </c>
       <c r="I55" s="29" t="s">
-        <v>95</v>
+        <v>335</v>
       </c>
       <c r="J55" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K55" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L55" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="N55" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="O55" s="33" t="n">
-        <v>1</v>
+        <v>107</v>
+      </c>
+      <c r="O55" s="29" t="s">
+        <v>329</v>
       </c>
       <c r="P55" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" s="29" t="s">
-        <v>293</v>
+      <c r="Q55" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" s="29" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6409,58 +6992,61 @@
         <v>46685</v>
       </c>
       <c r="C56" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="D56" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>250</v>
-      </c>
       <c r="F56" s="43" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="H56" s="43" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>105</v>
       </c>
       <c r="I56" s="43" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J56" s="43" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K56" s="43" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L56" s="43" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="M56" s="43" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="N56" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="O56" s="45" t="n">
+        <v>107</v>
+      </c>
+      <c r="O56" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="P56" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="P56" s="45" t="n">
+      <c r="Q56" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" s="43" t="s">
-        <v>295</v>
+      <c r="R56" s="43" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="46" t="s">
-        <v>296</v>
+      <c r="A58" s="47" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q56"/>
+  <autoFilter ref="A4:R56"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6478,67 +7064,815 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C5&amp;"*")</f>
+        <v>9</v>
+      </c>
+      <c r="G5" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C5&amp;"*"),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G5,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C6&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="G6" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C6&amp;"*"),"")</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G6,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C7&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C7&amp;"*"),"")</f>
+        <v>3</v>
+      </c>
+      <c r="H7" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G7,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>361</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C8&amp;"*")</f>
+        <v>7</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C8&amp;"*"),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G8,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>363</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C9&amp;"*")</f>
+        <v>9</v>
+      </c>
+      <c r="G9" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C9&amp;"*"),"")</f>
+        <v>6</v>
+      </c>
+      <c r="H9" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G9,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>366</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>367</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C10&amp;"*")</f>
+        <v>6</v>
+      </c>
+      <c r="G10" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C10&amp;"*"),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G10,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>369</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C11&amp;"*")</f>
+        <v>8</v>
+      </c>
+      <c r="G11" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C11&amp;"*"),"")</f>
+        <v>6</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G11,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C12&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="G12" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C12&amp;"*"),"")</f>
+        <v>7</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G12,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>375</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C13&amp;"*")</f>
+        <v>6</v>
+      </c>
+      <c r="G13" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C13&amp;"*"),"")</f>
+        <v>15</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G13,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46426</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>379</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C14&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G14" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C14&amp;"*"),"")</f>
+        <v>15</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G14,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46426</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>380</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C15&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G15" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C15&amp;"*"),"")</f>
+        <v>18</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G15,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C16&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G16" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C16&amp;"*"),"")</f>
+        <v>19</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G16,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>385</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>386</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>387</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C17&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="G17" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C17&amp;"*"),"")</f>
+        <v>19</v>
+      </c>
+      <c r="H17" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G17,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>388</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C18&amp;"*")</f>
+        <v>6</v>
+      </c>
+      <c r="G18" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C18&amp;"*"),"")</f>
+        <v>4</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G18,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>391</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C19&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G19" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C19&amp;"*"),"")</f>
+        <v>7</v>
+      </c>
+      <c r="H19" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G19,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>394</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>395</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C20&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="G20" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C20&amp;"*"),"")</f>
+        <v>10</v>
+      </c>
+      <c r="H20" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G20,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C21&amp;"*")</f>
+        <v>3</v>
+      </c>
+      <c r="G21" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C21&amp;"*"),"")</f>
+        <v>13</v>
+      </c>
+      <c r="H21" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G21,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46412</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>399</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>400</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>401</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C22&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G22" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C22&amp;"*"),"")</f>
+        <v>10</v>
+      </c>
+      <c r="H22" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G22,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>402</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>403</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>404</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C23&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="G23" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C23&amp;"*"),"")</f>
+        <v>10</v>
+      </c>
+      <c r="H23" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G23,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>405</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>406</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C24&amp;"*")</f>
+        <v>6</v>
+      </c>
+      <c r="G24" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C24&amp;"*"),"")</f>
+        <v>11</v>
+      </c>
+      <c r="H24" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G24,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C25&amp;"*")</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C25&amp;"*"),"")</f>
+        <v>11</v>
+      </c>
+      <c r="H25" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G25,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>412</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>413</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C26&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G26" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C26&amp;"*"),"")</f>
+        <v>11</v>
+      </c>
+      <c r="H26" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G26,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="51" t="n">
+        <f aca="false">COUNTIF('Year Plan'!$H$5:$H$56,"*"&amp;C27&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="G27" s="51" t="n">
+        <f aca="false">IFERROR(_xlfn.MINIFS('Year Plan'!$A$5:$A$56,'Year Plan'!$H$5:$H$56,"*"&amp;C27&amp;"*"),"")</f>
+        <v>13</v>
+      </c>
+      <c r="H27" s="52" t="n">
+        <f aca="false">IFERROR(INDEX('Year Plan'!$B$5:$B$56,MATCH(G27,'Year Plan'!$A$5:$A$56,0)),"")</f>
+        <v>46412</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <f aca="false">COUNTIF(F5:F27,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="47" t="s">
+        <v>418</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>299</v>
+        <v>421</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>300</v>
+        <v>422</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>301</v>
+        <v>423</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>302</v>
+        <v>424</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>303</v>
+        <v>425</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>304</v>
+        <v>426</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>305</v>
+        <v>427</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>306</v>
+        <v>428</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>307</v>
+        <v>429</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>308</v>
+        <v>430</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6549,34 +7883,37 @@
         <v>46328</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>309</v>
+        <v>432</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>311</v>
+        <v>433</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>312</v>
+        <v>434</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>313</v>
+        <v>435</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>314</v>
+        <v>436</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>315</v>
+        <v>437</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>316</v>
+        <v>438</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6587,34 +7924,37 @@
         <v>46335</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>317</v>
+        <v>440</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>318</v>
+        <v>65</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>319</v>
+        <v>441</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>320</v>
+        <v>442</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>321</v>
+        <v>443</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>322</v>
+        <v>444</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>323</v>
+        <v>445</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>324</v>
+        <v>446</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6625,34 +7965,37 @@
         <v>46342</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>325</v>
+        <v>448</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>326</v>
+        <v>71</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>329</v>
+        <v>451</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>330</v>
+        <v>452</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>331</v>
+        <v>453</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>332</v>
+        <v>454</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6663,34 +8006,37 @@
         <v>46349</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>333</v>
+        <v>456</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>335</v>
+        <v>457</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>336</v>
+        <v>458</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>337</v>
+        <v>459</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>339</v>
+        <v>461</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>340</v>
+        <v>462</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6701,34 +8047,37 @@
         <v>46356</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>341</v>
+        <v>464</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>343</v>
+        <v>465</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>344</v>
+        <v>466</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>345</v>
+        <v>467</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>346</v>
+        <v>468</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>347</v>
+        <v>469</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>348</v>
+        <v>470</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6739,34 +8088,37 @@
         <v>46363</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>350</v>
+        <v>93</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>351</v>
+        <v>472</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>352</v>
+        <v>473</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>353</v>
+        <v>474</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>354</v>
+        <v>475</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>355</v>
+        <v>476</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>356</v>
+        <v>477</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6777,34 +8129,37 @@
         <v>46370</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>357</v>
+        <v>479</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>358</v>
+        <v>99</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>359</v>
+        <v>480</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>361</v>
+        <v>482</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>362</v>
+        <v>483</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>363</v>
+        <v>484</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>364</v>
+        <v>485</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6815,34 +8170,37 @@
         <v>46377</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>365</v>
+        <v>487</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>366</v>
+        <v>105</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>95</v>
+        <v>488</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6853,34 +8211,37 @@
         <v>46391</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>367</v>
+        <v>489</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>368</v>
+        <v>115</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>369</v>
+        <v>490</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>370</v>
+        <v>491</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>371</v>
+        <v>492</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>372</v>
+        <v>493</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>373</v>
+        <v>494</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>374</v>
+        <v>495</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6891,34 +8252,37 @@
         <v>46398</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>376</v>
+        <v>123</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>377</v>
+        <v>498</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>378</v>
+        <v>499</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>380</v>
+        <v>501</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>381</v>
+        <v>502</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>382</v>
+        <v>503</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6929,34 +8293,37 @@
         <v>46405</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>385</v>
+        <v>505</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>386</v>
+        <v>506</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>387</v>
+        <v>507</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>388</v>
+        <v>508</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>389</v>
+        <v>509</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>390</v>
+        <v>510</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6967,34 +8334,37 @@
         <v>46412</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>391</v>
+        <v>512</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>392</v>
+        <v>134</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>393</v>
+        <v>513</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>394</v>
+        <v>514</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>396</v>
+        <v>516</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>397</v>
+        <v>517</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>398</v>
+        <v>518</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7005,34 +8375,37 @@
         <v>46419</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>399</v>
+        <v>520</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>400</v>
+        <v>143</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>401</v>
+        <v>521</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>402</v>
+        <v>522</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>403</v>
+        <v>523</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>404</v>
+        <v>524</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>405</v>
+        <v>525</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>406</v>
+        <v>526</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7043,34 +8416,37 @@
         <v>46426</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>407</v>
+        <v>528</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>409</v>
+        <v>529</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>411</v>
+        <v>531</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>412</v>
+        <v>532</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>405</v>
+        <v>533</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>413</v>
+        <v>526</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7081,34 +8457,37 @@
         <v>46433</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>414</v>
+        <v>535</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>415</v>
+        <v>157</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>416</v>
+        <v>536</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>417</v>
+        <v>537</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>418</v>
+        <v>538</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>419</v>
+        <v>539</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>405</v>
+        <v>540</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>420</v>
+        <v>526</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7119,34 +8498,37 @@
         <v>46440</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>421</v>
+        <v>542</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>422</v>
+        <v>162</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>423</v>
+        <v>543</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>424</v>
+        <v>544</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>425</v>
+        <v>545</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>426</v>
+        <v>546</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>405</v>
+        <v>547</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>427</v>
+        <v>526</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7157,34 +8539,37 @@
         <v>46447</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>428</v>
+        <v>549</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>429</v>
+        <v>172</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>430</v>
+        <v>550</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>431</v>
+        <v>551</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>432</v>
+        <v>552</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>433</v>
+        <v>553</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>434</v>
+        <v>554</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>435</v>
+        <v>555</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7195,34 +8580,37 @@
         <v>46454</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>436</v>
+        <v>557</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>437</v>
+        <v>181</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>438</v>
+        <v>558</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>439</v>
+        <v>559</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>440</v>
+        <v>560</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>441</v>
+        <v>561</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>434</v>
+        <v>562</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>442</v>
+        <v>555</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7233,34 +8621,37 @@
         <v>46461</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>443</v>
+        <v>564</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>444</v>
+        <v>187</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>445</v>
+        <v>565</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>446</v>
+        <v>566</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>447</v>
+        <v>567</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>448</v>
+        <v>568</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>434</v>
+        <v>569</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>449</v>
+        <v>555</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7271,34 +8662,37 @@
         <v>46468</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>450</v>
+        <v>571</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>451</v>
+        <v>193</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>452</v>
+        <v>572</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>453</v>
+        <v>573</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>454</v>
+        <v>574</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>455</v>
+        <v>575</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>434</v>
+        <v>576</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>456</v>
+        <v>555</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7309,34 +8703,37 @@
         <v>46475</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>457</v>
+        <v>578</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>458</v>
+        <v>198</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>459</v>
+        <v>579</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>461</v>
+        <v>581</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>462</v>
+        <v>582</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>434</v>
+        <v>583</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>463</v>
+        <v>555</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7347,34 +8744,37 @@
         <v>46482</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>464</v>
+        <v>585</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>465</v>
+        <v>206</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>466</v>
+        <v>586</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>467</v>
+        <v>587</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>468</v>
+        <v>588</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>469</v>
+        <v>589</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>434</v>
+        <v>590</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>470</v>
+        <v>555</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7385,34 +8785,37 @@
         <v>46489</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>471</v>
+        <v>592</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>472</v>
+        <v>212</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>473</v>
+        <v>593</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>474</v>
+        <v>594</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>475</v>
+        <v>595</v>
       </c>
       <c r="J27" s="23" t="s">
-        <v>476</v>
+        <v>596</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>434</v>
+        <v>597</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>477</v>
+        <v>555</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7423,34 +8826,37 @@
         <v>46496</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>478</v>
+        <v>599</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>479</v>
+        <v>218</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>481</v>
+        <v>601</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>482</v>
+        <v>602</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>483</v>
+        <v>603</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>434</v>
+        <v>604</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>484</v>
+        <v>555</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7461,34 +8867,37 @@
         <v>46503</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>485</v>
+        <v>606</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>486</v>
+        <v>224</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>487</v>
+        <v>607</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>488</v>
+        <v>608</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>489</v>
+        <v>609</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>490</v>
+        <v>610</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>434</v>
+        <v>611</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>491</v>
+        <v>555</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7499,34 +8908,37 @@
         <v>46510</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>492</v>
+        <v>613</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>493</v>
+        <v>233</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>494</v>
+        <v>614</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>495</v>
+        <v>615</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>496</v>
+        <v>616</v>
       </c>
       <c r="J30" s="29" t="s">
-        <v>497</v>
+        <v>617</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>434</v>
+        <v>618</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>498</v>
+        <v>555</v>
+      </c>
+      <c r="M30" s="29" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7537,34 +8949,37 @@
         <v>46517</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>450</v>
+        <v>571</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>499</v>
+        <v>240</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>500</v>
+        <v>620</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>501</v>
+        <v>621</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>502</v>
+        <v>622</v>
       </c>
       <c r="J31" s="29" t="s">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="K31" s="29" t="s">
-        <v>434</v>
+        <v>624</v>
       </c>
       <c r="L31" s="29" t="s">
-        <v>504</v>
+        <v>555</v>
+      </c>
+      <c r="M31" s="29" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7575,34 +8990,37 @@
         <v>46524</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>505</v>
+        <v>626</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>506</v>
+        <v>243</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>507</v>
+        <v>627</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>508</v>
+        <v>628</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>509</v>
+        <v>629</v>
       </c>
       <c r="J32" s="29" t="s">
-        <v>510</v>
+        <v>630</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>434</v>
+        <v>631</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>511</v>
+        <v>555</v>
+      </c>
+      <c r="M32" s="29" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7613,34 +9031,37 @@
         <v>46531</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>512</v>
+        <v>633</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>513</v>
+        <v>247</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>514</v>
+        <v>634</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>515</v>
+        <v>635</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>516</v>
+        <v>636</v>
       </c>
       <c r="J33" s="29" t="s">
-        <v>517</v>
+        <v>637</v>
       </c>
       <c r="K33" s="29" t="s">
-        <v>434</v>
+        <v>638</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>518</v>
+        <v>555</v>
+      </c>
+      <c r="M33" s="29" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7651,34 +9072,37 @@
         <v>46538</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>519</v>
+        <v>640</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>520</v>
+        <v>252</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>521</v>
+        <v>641</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>522</v>
+        <v>642</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>523</v>
+        <v>643</v>
       </c>
       <c r="J34" s="29" t="s">
-        <v>524</v>
+        <v>644</v>
       </c>
       <c r="K34" s="29" t="s">
-        <v>434</v>
+        <v>645</v>
       </c>
       <c r="L34" s="29" t="s">
-        <v>525</v>
+        <v>555</v>
+      </c>
+      <c r="M34" s="29" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7689,34 +9113,37 @@
         <v>46545</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>526</v>
+        <v>647</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>527</v>
+        <v>258</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>528</v>
+        <v>648</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>529</v>
+        <v>649</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>530</v>
+        <v>650</v>
       </c>
       <c r="J35" s="29" t="s">
-        <v>531</v>
+        <v>651</v>
       </c>
       <c r="K35" s="29" t="s">
-        <v>434</v>
+        <v>652</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>532</v>
+        <v>555</v>
+      </c>
+      <c r="M35" s="29" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7727,34 +9154,37 @@
         <v>46552</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>533</v>
+        <v>654</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>534</v>
+        <v>262</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>535</v>
+        <v>655</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>536</v>
+        <v>656</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>537</v>
+        <v>657</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>538</v>
+        <v>658</v>
       </c>
       <c r="K36" s="29" t="s">
-        <v>434</v>
+        <v>659</v>
       </c>
       <c r="L36" s="29" t="s">
-        <v>539</v>
+        <v>555</v>
+      </c>
+      <c r="M36" s="29" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7765,34 +9195,37 @@
         <v>46559</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>540</v>
+        <v>661</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>541</v>
+        <v>123</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>542</v>
+        <v>662</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>543</v>
+        <v>663</v>
       </c>
       <c r="I37" s="29" t="s">
-        <v>544</v>
+        <v>664</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>545</v>
+        <v>665</v>
       </c>
       <c r="K37" s="29" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>546</v>
+        <v>555</v>
+      </c>
+      <c r="M37" s="29" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7803,34 +9236,37 @@
         <v>46566</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>547</v>
+        <v>668</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>548</v>
+        <v>267</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>549</v>
+        <v>669</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>550</v>
+        <v>670</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>551</v>
+        <v>671</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>503</v>
+        <v>672</v>
       </c>
       <c r="K38" s="29" t="s">
-        <v>434</v>
+        <v>624</v>
       </c>
       <c r="L38" s="29" t="s">
-        <v>463</v>
+        <v>555</v>
+      </c>
+      <c r="M38" s="29" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7841,34 +9277,37 @@
         <v>46573</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>552</v>
+        <v>673</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>553</v>
+        <v>276</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>554</v>
+        <v>674</v>
       </c>
       <c r="H39" s="37" t="s">
+        <v>675</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>676</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>677</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>678</v>
+      </c>
+      <c r="L39" s="37" t="s">
         <v>555</v>
       </c>
-      <c r="I39" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="J39" s="37" t="s">
-        <v>557</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L39" s="37" t="s">
-        <v>558</v>
+      <c r="M39" s="37" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7879,34 +9318,37 @@
         <v>46580</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>559</v>
+        <v>680</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>561</v>
+        <v>681</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>495</v>
+        <v>682</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>562</v>
+        <v>616</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>563</v>
+        <v>683</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>434</v>
+        <v>684</v>
       </c>
       <c r="L40" s="37" t="s">
-        <v>564</v>
+        <v>555</v>
+      </c>
+      <c r="M40" s="37" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7917,34 +9359,37 @@
         <v>46601</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>565</v>
+        <v>686</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>566</v>
+        <v>288</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>567</v>
+        <v>687</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>495</v>
+        <v>688</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>568</v>
+        <v>616</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>545</v>
+        <v>689</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L41" s="37" t="s">
-        <v>569</v>
+        <v>555</v>
+      </c>
+      <c r="M41" s="37" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7955,34 +9400,37 @@
         <v>46608</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>570</v>
+        <v>691</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>571</v>
+        <v>296</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>572</v>
+        <v>692</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>573</v>
+        <v>693</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>574</v>
+        <v>694</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>575</v>
+        <v>695</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>434</v>
+        <v>696</v>
       </c>
       <c r="L42" s="37" t="s">
-        <v>576</v>
+        <v>555</v>
+      </c>
+      <c r="M42" s="37" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7993,34 +9441,37 @@
         <v>46615</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>577</v>
+        <v>698</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>578</v>
+        <v>299</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>579</v>
+        <v>699</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>573</v>
+        <v>700</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>580</v>
+        <v>694</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>581</v>
+        <v>701</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>434</v>
+        <v>702</v>
       </c>
       <c r="L43" s="37" t="s">
-        <v>582</v>
+        <v>555</v>
+      </c>
+      <c r="M43" s="37" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8031,34 +9482,37 @@
         <v>46622</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>583</v>
+        <v>704</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>584</v>
+        <v>302</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>585</v>
+        <v>705</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>573</v>
+        <v>706</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>523</v>
+        <v>694</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>434</v>
+        <v>707</v>
       </c>
       <c r="L44" s="37" t="s">
-        <v>587</v>
+        <v>555</v>
+      </c>
+      <c r="M44" s="37" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8069,34 +9523,37 @@
         <v>46629</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>588</v>
+        <v>709</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>589</v>
+        <v>305</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>535</v>
+        <v>710</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>536</v>
+        <v>656</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>537</v>
+        <v>657</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>586</v>
+        <v>658</v>
       </c>
       <c r="K45" s="37" t="s">
-        <v>434</v>
+        <v>707</v>
       </c>
       <c r="L45" s="37" t="s">
-        <v>590</v>
+        <v>555</v>
+      </c>
+      <c r="M45" s="37" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8107,34 +9564,37 @@
         <v>46636</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>591</v>
+        <v>712</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>592</v>
+        <v>313</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>593</v>
+        <v>713</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>495</v>
+        <v>714</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>595</v>
+        <v>715</v>
       </c>
       <c r="K46" s="29" t="s">
-        <v>434</v>
+        <v>716</v>
       </c>
       <c r="L46" s="29" t="s">
-        <v>596</v>
+        <v>555</v>
+      </c>
+      <c r="M46" s="29" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8145,34 +9605,37 @@
         <v>46643</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>597</v>
+        <v>718</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>598</v>
+        <v>318</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>599</v>
+        <v>719</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>573</v>
+        <v>720</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>600</v>
+        <v>694</v>
       </c>
       <c r="J47" s="29" t="s">
-        <v>595</v>
+        <v>721</v>
       </c>
       <c r="K47" s="29" t="s">
-        <v>434</v>
+        <v>716</v>
       </c>
       <c r="L47" s="29" t="s">
-        <v>601</v>
+        <v>555</v>
+      </c>
+      <c r="M47" s="29" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8183,34 +9646,37 @@
         <v>46650</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>602</v>
+        <v>723</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>153</v>
+        <v>320</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>603</v>
+        <v>172</v>
       </c>
       <c r="G48" s="29" t="s">
-        <v>528</v>
+        <v>724</v>
       </c>
       <c r="H48" s="29" t="s">
-        <v>529</v>
+        <v>649</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
       <c r="J48" s="29" t="s">
-        <v>545</v>
+        <v>725</v>
       </c>
       <c r="K48" s="29" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L48" s="29" t="s">
-        <v>532</v>
+        <v>555</v>
+      </c>
+      <c r="M48" s="29" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8221,34 +9687,37 @@
         <v>46657</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>605</v>
+        <v>726</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>281</v>
+        <v>92</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>606</v>
+        <v>322</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>549</v>
+        <v>727</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>607</v>
+        <v>670</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>608</v>
+        <v>728</v>
       </c>
       <c r="J49" s="29" t="s">
-        <v>545</v>
+        <v>729</v>
       </c>
       <c r="K49" s="29" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L49" s="29" t="s">
-        <v>609</v>
+        <v>555</v>
+      </c>
+      <c r="M49" s="29" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8259,34 +9728,37 @@
         <v>46664</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>610</v>
+        <v>731</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>611</v>
+        <v>326</v>
       </c>
       <c r="G50" s="29" t="s">
-        <v>612</v>
+        <v>732</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>285</v>
+        <v>733</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>613</v>
+        <v>327</v>
       </c>
       <c r="J50" s="29" t="s">
-        <v>545</v>
+        <v>734</v>
       </c>
       <c r="K50" s="29" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L50" s="29" t="s">
-        <v>614</v>
+        <v>555</v>
+      </c>
+      <c r="M50" s="29" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8297,34 +9769,37 @@
         <v>46671</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>615</v>
+        <v>736</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="F51" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>737</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>738</v>
+      </c>
+      <c r="I51" s="29" t="s">
         <v>616</v>
       </c>
-      <c r="G51" s="29" t="s">
-        <v>617</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>495</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>618</v>
-      </c>
       <c r="J51" s="29" t="s">
-        <v>545</v>
+        <v>739</v>
       </c>
       <c r="K51" s="29" t="s">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="L51" s="29" t="s">
-        <v>619</v>
+        <v>555</v>
+      </c>
+      <c r="M51" s="29" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8335,38 +9810,41 @@
         <v>46678</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>620</v>
+        <v>741</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>292</v>
+        <v>105</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>95</v>
+        <v>335</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H52" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>621</v>
+        <v>105</v>
       </c>
       <c r="J52" s="29" t="s">
-        <v>95</v>
+        <v>742</v>
       </c>
       <c r="K52" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L52" s="29" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="M52" s="29" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L52"/>
+  <autoFilter ref="A4:M52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8378,7 +9856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8397,201 +9875,201 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>622</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>623</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>625</v>
+        <v>746</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>626</v>
+        <v>350</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>627</v>
+        <v>747</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>628</v>
+        <v>748</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>629</v>
+        <v>749</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
-        <v>631</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>632</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>633</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>634</v>
+      <c r="A5" s="49" t="s">
+        <v>751</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>752</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>753</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>635</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>636</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>637</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>638</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>640</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>641</v>
+      <c r="A6" s="49" t="s">
+        <v>755</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>757</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>758</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>759</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>760</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>642</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>643</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>644</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>645</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>646</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>647</v>
-      </c>
-      <c r="G7" s="48" t="s">
-        <v>648</v>
+      <c r="A7" s="49" t="s">
+        <v>762</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>763</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>765</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>766</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>767</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>649</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>650</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>651</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>652</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>653</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>647</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>654</v>
+      <c r="A8" s="49" t="s">
+        <v>769</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>770</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>771</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>772</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>773</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>767</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47" t="s">
-        <v>655</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>656</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>657</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>658</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>659</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>660</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>661</v>
+      <c r="A9" s="49" t="s">
+        <v>775</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>776</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>777</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>778</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>779</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>780</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="47" t="s">
-        <v>662</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>663</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>633</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>664</v>
+      <c r="A10" s="49" t="s">
+        <v>782</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>783</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>753</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
-        <v>665</v>
-      </c>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="49" t="s">
+        <v>785</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>786</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>787</v>
+      </c>
+      <c r="D11" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>667</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>545</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>668</v>
+      <c r="E11" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>669</v>
+      <c r="A13" s="56" t="s">
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -8605,7 +10083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8623,297 +10101,297 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>790</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>671</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>672</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>673</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>674</v>
-      </c>
-      <c r="G4" s="50" t="s">
-        <v>675</v>
+        <v>792</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>793</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>794</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="51" t="n">
+      <c r="A5" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A5)</f>
         <v>9</v>
       </c>
-      <c r="D5" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D5" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3</v>
       </c>
-      <c r="F5" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F5" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>2</v>
       </c>
-      <c r="G5" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G5" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D5,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="51" t="n">
+      <c r="A6" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A6)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D6" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$P$5:$P$56),0)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F6" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>1.5</v>
       </c>
-      <c r="G6" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G6" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D6,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="51" t="n">
+      <c r="A7" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A7)</f>
         <v>9</v>
       </c>
-      <c r="D7" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D7" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3.5</v>
       </c>
-      <c r="F7" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F7" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>3</v>
       </c>
-      <c r="G7" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G7" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D7,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="51" t="n">
+      <c r="A8" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A8)</f>
         <v>9</v>
       </c>
-      <c r="D8" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D8,'Year Plan'!$O$5:$O$56),0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="F8" s="52" t="n">
+      <c r="D8" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="59" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D8,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3.5</v>
       </c>
-      <c r="G8" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D8,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="F8" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D8,'Year Plan'!$Q$5:$Q$56),0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D8,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="51" t="n">
+      <c r="A9" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A9)</f>
         <v>9</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D9" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$P$5:$P$56),0)</f>
         <v>4.5</v>
       </c>
-      <c r="F9" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F9" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>3.5</v>
       </c>
-      <c r="G9" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G9" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D9,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="51" t="n">
+      <c r="A10" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A10)</f>
         <v>7</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D10" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3.5</v>
       </c>
-      <c r="F10" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F10" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>4</v>
       </c>
-      <c r="G10" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G10" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D10,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="51" t="n">
+      <c r="A11" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="58" t="n">
         <f aca="false">COUNTIF('Year Plan'!$D$5:$D$56,A11)</f>
         <v>1</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D11" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3</v>
       </c>
-      <c r="F11" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F11" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>4.5</v>
       </c>
-      <c r="G11" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G11" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D11,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>676</v>
+        <v>796</v>
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>52</v>
       </c>
-      <c r="D12" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D12" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F12" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>4.5</v>
       </c>
-      <c r="G12" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G12" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D12,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D13" s="58" t="s">
+        <v>271</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$P$5:$P$56),0)</f>
         <v>1.25</v>
       </c>
-      <c r="F13" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F13" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>2</v>
       </c>
-      <c r="G13" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G13" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D13,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="51" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D14" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3.5</v>
       </c>
-      <c r="F14" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F14" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>4</v>
       </c>
-      <c r="G14" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G14" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D14,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="E15" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D15" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$P$5:$P$56),0)</f>
         <v>3</v>
       </c>
-      <c r="F15" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F15" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>4.5</v>
       </c>
-      <c r="G15" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G15" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D15,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="51" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$O$5:$O$56),0)</f>
+      <c r="D16" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$P$5:$P$56),0)</f>
         <v>1.25</v>
       </c>
-      <c r="F16" s="52" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$P$5:$P$56),0)</f>
+      <c r="F16" s="59" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$Q$5:$Q$56),0)</f>
         <v>1.75</v>
       </c>
-      <c r="G16" s="51" t="n">
-        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$O$5:$O$56,"&gt;0")</f>
+      <c r="G16" s="58" t="n">
+        <f aca="false">COUNTIFS('Year Plan'!$C$5:$C$56,D16,'Year Plan'!$P$5:$P$56,"&gt;0")</f>
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="46" t="s">
-        <v>677</v>
+      <c r="D18" s="47" t="s">
+        <v>797</v>
       </c>
     </row>
   </sheetData>
